--- a/docs/examples/47-dataframe-io-styling/output/regional-sales.xlsx
+++ b/docs/examples/47-dataframe-io-styling/output/regional-sales.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
   <si>
     <t>orderDate</t>
   </si>
